--- a/naver-place-crawler/results_health/연제구_PT.xlsx
+++ b/naver-place-crawler/results_health/연제구_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>래피드스튜디오GYM</t>
+          <t>인트로피트니스 연산점 24시 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rapidstudio@naver.com</t>
+          <t>intro_fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1422-3351</t>
+          <t>0507-1490-9696</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 20 이레빌딩 6층</t>
+          <t>부산광역시 연제구 반송로 89 BS89빌딩 5층 인트로피트니스 연산점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapidstudio</t>
+          <t>https://blog.naver.com/intro_fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>105</v>
+        <v>506</v>
       </c>
       <c r="Q2" t="n">
-        <v>276</v>
+        <v>522</v>
       </c>
       <c r="R2" t="n">
-        <v>381</v>
+        <v>1028</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>36084249</t>
+          <t>1710235102</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36084249</t>
+          <t>https://m.place.naver.com/place/1710235102</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24시헬스포유</t>
+          <t>스페이스PT&amp;헬스 시청연산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>groupcircuit@naver.com</t>
+          <t>spacept@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1345-8648</t>
+          <t>0507-1498-7935</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 미남로 11 영주빌딩 4층</t>
+          <t>부산광역시 연제구 중앙대로 1077 12층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/groupcircuit</t>
+          <t>https://open.kakao.com/o/sjo5jMMf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>306</v>
       </c>
       <c r="R3" t="n">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1065272252</t>
+          <t>2018417908</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065272252</t>
+          <t>https://m.place.naver.com/place/2018417908</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q4" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,46 +834,46 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밀리오레피트니스 PT</t>
+          <t>제이엠드림핏 헬스&amp;PT, 태닝 연산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>migliorept@naver.com</t>
+          <t>ninopjd@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-8260</t>
+          <t>051-751-7910</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 219 6층</t>
+          <t>부산광역시 연제구 과정로 180 엠타워상가 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/migliorefitness_pt</t>
+          <t>https://blog.naver.com/ninopjd</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="Q5" t="n">
-        <v>111</v>
+        <v>308</v>
       </c>
       <c r="R5" t="n">
-        <v>265</v>
+        <v>568</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +918,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1934153220</t>
+          <t>1891543405</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934153220</t>
+          <t>https://m.place.naver.com/place/1891543405</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피티파크</t>
+          <t>마이루틴짐 부산시청점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jin12633@naver.com</t>
+          <t>myroutinegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-6191</t>
+          <t>0507-1353-4618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 90 2층</t>
+          <t>부산광역시 연제구 거제시장로 42 4층 마이루틴짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p.t_park/</t>
+          <t>https://litt.ly/myroutine</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="Q6" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="R6" t="n">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1326156865</t>
+          <t>1684941372</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326156865</t>
+          <t>https://m.place.naver.com/place/1684941372</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1116,41 +1116,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피티가치 시청연산점</t>
+          <t>무지개휘트니스 연산점 헬스&amp;PT&amp;GX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chanju3795@naver.com</t>
+          <t>rainbow4445@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1408-7550</t>
+          <t>051-868-6880</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1043 정인빌딩 5층 피티가치 시청연산점</t>
+          <t>부산광역시 연제구 중앙대로 1090 5층 무지개휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_gachi_cityhall?igshid=MzRlODBiNWFlZA==</t>
+          <t>https://blog.naver.com/rainbow4445</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>224</v>
+        <v>941</v>
       </c>
       <c r="Q8" t="n">
-        <v>602</v>
+        <v>968</v>
       </c>
       <c r="R8" t="n">
-        <v>826</v>
+        <v>1909</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1606361593</t>
+          <t>1247782660</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1606361593</t>
+          <t>https://m.place.naver.com/place/1247782660</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>자연안에PT스튜디오</t>
+          <t>목림휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sdud6040@naver.com</t>
+          <t>moklim24-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1429-8805</t>
+          <t>051-862-5599</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 141</t>
+          <t>부산광역시 연제구 중앙대로1043번길 50 7층 헬스장</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.naturept.co.kr/</t>
+          <t>https://open.kakao.com/o/sMBjNGCc</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="R9" t="n">
-        <v>60</v>
+        <v>219</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>38757600</t>
+          <t>1186681639</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38757600</t>
+          <t>https://m.place.naver.com/place/1186681639</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에센셜 필라테스 요가 연산점</t>
+          <t>피티파크</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>essentialstudi0@naver.com</t>
+          <t>jin12633@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1468-1440</t>
+          <t>0507-1350-6191</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 81-17 2층</t>
+          <t>부산광역시 연제구 중앙천로 90 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/essentialstudi0</t>
+          <t>https://www.instagram.com/p.t_park/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R10" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1083537653</t>
+          <t>1326156865</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083537653</t>
+          <t>https://m.place.naver.com/place/1326156865</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>피부,체형관리</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>벨라테스앤피티</t>
+          <t>머슬하모니</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bellates_pt@naver.com</t>
+          <t>muscleharmony@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-3106</t>
+          <t>051-913-1117</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 42 2층</t>
+          <t>부산광역시 연제구 신촌로 51 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bellates_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1187844272</t>
+          <t>1819908137</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187844272</t>
+          <t>https://m.place.naver.com/place/1819908137</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사나이짐</t>
+          <t>국제휘트니스 &amp; PT 교대점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sanaigym@naver.com</t>
+          <t>kukje_fitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1330-4707</t>
+          <t>0507-1496-7969</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로278번길 47 2층(연산동)</t>
+          <t>부산광역시 연제구 중앙대로 1217 국제빌딩 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sanaigym</t>
+          <t>https://www.youtube.com/@%EA%B5%AD%ED%97%AC%EB%B6%80%EC%82%B0%EA%B5%90%EB%8C%80%EC%A0%90</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>145</v>
+        <v>479</v>
       </c>
       <c r="Q12" t="n">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="R12" t="n">
-        <v>590</v>
+        <v>975</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,56 +1576,56 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1554315770</t>
+          <t>32565643</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1554315770</t>
+          <t>https://m.place.naver.com/place/32565643</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>목림휘트니스</t>
+          <t>리오 피트니스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>moklim24-@naver.com</t>
+          <t>ever6486@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>051-862-5599</t>
+          <t>0507-1378-8377</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 50 7층 헬스장</t>
+          <t>부산광역시 연제구 월드컵대로 128 지하 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sMBjNGCc</t>
+          <t>https://www.instagram.com/mad_leofitness?igsh=MXNmY2RwYzRmNm9sZA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>218</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>219</v>
+        <v>37</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,51 +1670,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1186681639</t>
+          <t>1808486603</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186681639</t>
+          <t>https://m.place.naver.com/place/1808486603</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>탑조이PT 연산점</t>
+          <t>바디메디필라테스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tnghks9702@naver.com</t>
+          <t>dreambodynsol_cn@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1489-9702</t>
+          <t>051-851-0111</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 3 B1층</t>
+          <t>부산광역시 연제구 연수로 130 상가A동 201호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s0__0hwan?igsh=cXg3b3kyem54dmky&amp;utm_source=qr</t>
+          <t>http://instagram.com/bodymedi_pilates</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="n">
-        <v>408</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>480</v>
+        <v>52</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1984112260</t>
+          <t>1421677552</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984112260</t>
+          <t>https://m.place.naver.com/place/1421677552</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1786,34 +1786,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>잼피티</t>
+          <t>엠씨피트니스&amp;기구필라테스 연산점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jam__pt@naver.com</t>
+          <t>mcfitnessyeonsan@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1423-9395</t>
+          <t>0507-1421-0460</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 150 3층</t>
+          <t>부산광역시 연제구 과정로 152 연산빌딩 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jam__pt</t>
+          <t>http://pf.kakao.com/_gdRSs/chat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1834,7 +1834,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>114</v>
+        <v>1100</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>791</v>
       </c>
       <c r="R15" t="n">
-        <v>144</v>
+        <v>1891</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,56 +1858,56 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1040929885</t>
+          <t>1678635952</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040929885</t>
+          <t>https://m.place.naver.com/place/1678635952</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>올바른운동 그룹PT 연산점</t>
+          <t>BK 킹스코트 GYM 연산점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>orbarn7@naver.com</t>
+          <t>bkkingscourtgym@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>051-867-5554</t>
+          <t>0507-1401-1205</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1089 B1층</t>
+          <t>부산광역시 연제구 연수로 144 2층 BK 킹스코트 GYM 연산점</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s0Rj5Jxh</t>
+          <t>https://blog.naver.com/bkkingscourtgym</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>116</v>
+        <v>582</v>
       </c>
       <c r="Q16" t="n">
-        <v>206</v>
+        <v>1070</v>
       </c>
       <c r="R16" t="n">
-        <v>322</v>
+        <v>1652</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,51 +1952,47 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1507343287</t>
+          <t>1664945924</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507343287</t>
+          <t>https://m.place.naver.com/place/1664945924</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>플러스휘트니스</t>
+          <t>킥앤핏스튜디오</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mantomansd@naver.com</t>
+          <t>schlgud@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1378-0170</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로3번길 32 플러스휘트니스</t>
+          <t>부산광역시 연제구 아시아드대로46번길 15 상가동 202호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kick_fit_studio?igsh=N3p3dmRsYm4wZWFr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2006,7 +2002,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2027,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,56 +2042,56 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>16698494</t>
+          <t>2007111294</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16698494</t>
+          <t>https://m.place.naver.com/place/2007111294</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>코오롱스포렉스 부산아시아드점</t>
+          <t>헤비핸즈복싱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kolon_sporex@naver.com</t>
+          <t>hardtokilll@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1474-5500</t>
+          <t>0507-1324-0652</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 종합운동장로 7 홈플러스 아시아드점 B2층</t>
+          <t>부산광역시 연제구 과정로 314 B동 3층 301호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.sporex.com/sub_branch/list_v.php?number=19</t>
+          <t>https://www.instagram.com/heavyhands_boxing</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2125,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1164725450</t>
+          <t>1403278642</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164725450</t>
+          <t>https://m.place.naver.com/place/1403278642</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2162,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BK 킹스코트 GYM 연산점 헬스&amp;PT</t>
+          <t>올데이짐 헬스&amp;PT 연산</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bkkingscourtgym@naver.com</t>
+          <t>babuperk1@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1401-1205</t>
+          <t>051-866-8834</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 144 2층 BK 킹스코트 GYM 연산점</t>
+          <t>부산광역시 연제구 과정로 256 3층 올데이짐</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bkkingscourtgym</t>
+          <t>https://blog.naver.com/babuperk1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2215,17 +2211,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>580</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>1060</v>
+        <v>22</v>
       </c>
       <c r="R19" t="n">
-        <v>1640</v>
+        <v>65</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1664945924</t>
+          <t>16717118</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664945924</t>
+          <t>https://m.place.naver.com/place/16717118</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2256,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제로짐 피티&amp;제로 필라테스</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>zerogym0@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1435-0111</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1033 메디컬빌딩 10층 제로필라테스/11층 제로짐</t>
+          <t>부산광역시 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zerogym0</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2313,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>89</v>
+        <v>1422</v>
       </c>
       <c r="Q20" t="n">
-        <v>941</v>
+        <v>1520</v>
       </c>
       <c r="R20" t="n">
-        <v>1030</v>
+        <v>2942</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,51 +2324,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1323116558</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323116558</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>에센셜 필라테스 요가 연산점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>essentialstudi0@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1468-1440</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 21 5층,6층</t>
+          <t>부산광역시 연제구 중앙천로 81-17 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/essentialstudi0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1415</v>
+        <v>116</v>
       </c>
       <c r="Q21" t="n">
-        <v>1516</v>
+        <v>62</v>
       </c>
       <c r="R21" t="n">
-        <v>2931</v>
+        <v>178</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,51 +2418,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1083537653</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1083537653</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>퍼스트밸런스 헬스&amp;PT&amp;GX 연산점</t>
+          <t>메디앤컬필라테스 연산점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>balancebody_sasang@naver.com</t>
+          <t>medincurl_official@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1412-2329</t>
+          <t>0507-1399-8042</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 25 노블레스스퀘어 B1층 퍼스트밸런스 연산</t>
+          <t>부산광역시 연제구 중앙대로 1091 901호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/firstbalance_center/</t>
+          <t>https://blog.naver.com/medincurl_official</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2481,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2501,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>118</v>
+        <v>867</v>
       </c>
       <c r="Q22" t="n">
-        <v>1024</v>
+        <v>892</v>
       </c>
       <c r="R22" t="n">
-        <v>1142</v>
+        <v>1759</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,51 +2512,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1163168113</t>
+          <t>36438582</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163168113</t>
+          <t>https://m.place.naver.com/place/36438582</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스 연산점</t>
+          <t>리드헬스&amp;PT&amp;기구필라테스 연산점24시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>medincurl_official@naver.com</t>
+          <t>lead8132@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1399-8042</t>
+          <t>0507-1356-8132</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1091 901호</t>
+          <t>부산광역시 연제구 고분로13번길 25 한창타워 3층 내 리드헬스(301호~303호)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/medincurl_official</t>
+          <t>https://www.instagram.com/lead_health.pt.pilates/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2575,7 +2571,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2595,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>861</v>
+        <v>702</v>
       </c>
       <c r="Q23" t="n">
-        <v>841</v>
+        <v>1578</v>
       </c>
       <c r="R23" t="n">
-        <v>1702</v>
+        <v>2280</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,47 +2606,51 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>36438582</t>
+          <t>1311686124</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36438582</t>
+          <t>https://m.place.naver.com/place/1311686124</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>어메이징골프아카데미</t>
+          <t>클라이 헬스PT 연산점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>aggolf@naver.com</t>
+          <t>positive_yun_@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1340-0936</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1042 12층, 13층, 14층</t>
+          <t>부산광역시 연제구 연수로 177 배산빌딩 4층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aggolf</t>
+          <t>https://blog.naver.com/positive_yun_</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>257</v>
+        <v>121</v>
       </c>
       <c r="Q24" t="n">
-        <v>73</v>
+        <v>793</v>
       </c>
       <c r="R24" t="n">
-        <v>330</v>
+        <v>914</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,56 +2700,52 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1876155285</t>
+          <t>1650784861</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876155285</t>
+          <t>https://m.place.naver.com/place/1650784861</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>마이루틴짐 부산시청점</t>
+          <t>코어핏 스튜디오 PT/헬스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>myroutinegym@naver.com</t>
+          <t>qkzp2447@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1353-4618</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제시장로 42 4층 마이루틴짐</t>
+          <t>부산광역시 연제구 세병로 16 한성기린아파트 상가3층 302호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://litt.ly/myroutine</t>
+          <t>https://youtube.com/@Bodysmith</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2779,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="R25" t="n">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,60 +2790,56 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1684941372</t>
+          <t>1238470397</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684941372</t>
+          <t>https://m.place.naver.com/place/1238470397</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>케어스튜디오 체형교정 &amp; PT</t>
+          <t>보답피트니스 시청 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>takho092753@naver.com</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>takho092753@gmail.com</t>
-        </is>
-      </c>
+          <t>fandomfit_cityhall@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1303-5542</t>
+          <t>0507-1311-8578</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1124번길 20 서진빌딩 3층 케어스튜디오</t>
+          <t>부산광역시 연제구 거제천로 94 6층, 7층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://physiograph.kr</t>
+          <t>https://www.instagram.com/bodapfitness</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2857,7 +2849,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2877,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>39</v>
+        <v>513</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>703</v>
       </c>
       <c r="R26" t="n">
-        <v>107</v>
+        <v>1216</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,47 +2884,51 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1088942032</t>
+          <t>1014850411</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088942032</t>
+          <t>https://m.place.naver.com/place/1014850411</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>247복싱</t>
+          <t>더리얼기구필라테스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>thaikick@naver.com</t>
+          <t>kch9728kkk@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>051-868-3948</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제대로 172</t>
+          <t>부산광역시 연제구 월드컵대로73번길 84 더리얼기구필라테스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thaikick/</t>
+          <t>https://www.instagram.com/therealpilates_pt/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2947,7 +2943,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,17 +2959,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="Q27" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="R27" t="n">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,52 +2978,56 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>501106950</t>
+          <t>1560928411</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/501106950</t>
+          <t>https://m.place.naver.com/place/1560928411</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SY피트니스짐</t>
+          <t>타임머신PT스튜디오</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>yong2ssem2@naver.com</t>
+          <t>kydkd7@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1402-6020</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 토곡로 29 2층</t>
+          <t>부산광역시 연제구 과정로 139 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/lgfitness/</t>
+          <t>https://blog.naver.com/kydkd7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3053,18 +3053,18 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
         <v>7</v>
       </c>
-      <c r="R28" t="n">
-        <v>10</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3072,51 +3072,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11368992</t>
+          <t>37038988</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11368992</t>
+          <t>https://m.place.naver.com/place/37038988</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>포바디짐</t>
+          <t>온스트레치 KN피트니스 법원점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>forbodygym@naver.com</t>
+          <t>njys2@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1476-0100</t>
+          <t>0507-1343-0432</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 258 연산해수피아 7층 포바디짐</t>
+          <t>부산광역시 연제구 법원로 2 3층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forbodygym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,51 +3166,51 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1142374938</t>
+          <t>2040167591</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142374938</t>
+          <t>https://m.place.naver.com/place/2040167591</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>카이트운동센터</t>
+          <t>템플짐 연산점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sonh9882@naver.com</t>
+          <t>alswl1933@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>051-867-7700</t>
+          <t>0507-1368-1876</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로32번길 24 2층</t>
+          <t>부산광역시 연제구 연수로 163 스타메디컬빌딩 8층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/alswl1933</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>39</v>
+        <v>504</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>378</v>
       </c>
       <c r="R30" t="n">
-        <v>43</v>
+        <v>882</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>37464088</t>
+          <t>2059297467</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37464088</t>
+          <t>https://m.place.naver.com/place/2059297467</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>클라이 헬스PT 연산점</t>
+          <t>포바디짐</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>positive_yun_@naver.com</t>
+          <t>forbodygym@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1340-0936</t>
+          <t>0507-1476-0100</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 177 배산빌딩 4층</t>
+          <t>부산광역시 연제구 거제천로 258 연산해수피아 7층 포바디짐</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/positive_yun_</t>
+          <t>https://blog.naver.com/forbodygym</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="Q31" t="n">
-        <v>791</v>
+        <v>101</v>
       </c>
       <c r="R31" t="n">
-        <v>906</v>
+        <v>119</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1650784861</t>
+          <t>1142374938</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650784861</t>
+          <t>https://m.place.naver.com/place/1142374938</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3376,29 +3376,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>노블레스짐 PT&amp;스트레칭</t>
+          <t>올바른운동 그룹PT 연산점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lllooo1024@naver.com</t>
+          <t>orbarn7@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1383-0097</t>
+          <t>051-867-5554</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 25 2층 220호</t>
+          <t>부산광역시 연제구 중앙대로 1089 B1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noblessegym</t>
+          <t>https://open.kakao.com/o/s0Rj5Jxh</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3424,7 +3424,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="Q32" t="n">
-        <v>398</v>
+        <v>205</v>
       </c>
       <c r="R32" t="n">
-        <v>429</v>
+        <v>321</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,51 +3448,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1152978393</t>
+          <t>1507343287</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1152978393</t>
+          <t>https://m.place.naver.com/place/1507343287</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>거제동 재활의신 타임피트니스 피티&amp;헬스장</t>
+          <t>플러스휘트니스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>time_fit@naver.com</t>
+          <t>mantomansd@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1493-3211</t>
+          <t>0507-1378-0170</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원로32번길 10 협성프라자 지하1층</t>
+          <t>부산광역시 연제구 월드컵대로3번길 32 플러스휘트니스</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/time_fit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1044928581</t>
+          <t>16698494</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044928581</t>
+          <t>https://m.place.naver.com/place/16698494</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3564,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>타임머신PT스튜디오</t>
+          <t>사나이짐</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kydkd7@naver.com</t>
+          <t>sanaigym@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1402-6020</t>
+          <t>0507-1330-4707</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 139 2층</t>
+          <t>부산광역시 연제구 과정로278번길 47 2층(연산동)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kydkd7</t>
+          <t>https://blog.naver.com/sanaigym</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>447</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>592</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3636,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37038988</t>
+          <t>1554315770</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37038988</t>
+          <t>https://m.place.naver.com/place/1554315770</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3658,34 +3658,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>팬덤짐PT</t>
+          <t>밀리오레피트니스 PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gusco2180@naver.com</t>
+          <t>migliorept@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1447-9683</t>
+          <t>0507-1337-8260</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 세병로 10-1 2층 연산동 PT 팬덤짐 PT 헬스</t>
+          <t>부산광역시 연제구 연수로 219 6층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gusco2180</t>
+          <t>https://litt.ly/migliorefitness_pt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q35" t="n">
-        <v>654</v>
+        <v>111</v>
       </c>
       <c r="R35" t="n">
-        <v>810</v>
+        <v>264</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3730,51 +3730,47 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1237805997</t>
+          <t>1934153220</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237805997</t>
+          <t>https://m.place.naver.com/place/1934153220</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>모션핏피트니스 헬스&amp;PT 연산토곡점</t>
+          <t>모두요가필라테스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>motionfit@naver.com</t>
+          <t>everybody_yp@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1353-5528</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연안로 19 2층</t>
+          <t>부산광역시 연제구 월드컵대로 221 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/motionfit.fitness/</t>
+          <t>https://www.instagram.com/modoo_yogapilates.barre</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3809,13 +3805,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>541</v>
+        <v>17</v>
       </c>
       <c r="Q36" t="n">
-        <v>211</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>752</v>
+        <v>22</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,17 +3820,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1531367968</t>
+          <t>2066412718</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531367968</t>
+          <t>https://m.place.naver.com/place/2066412718</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3846,34 +3842,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>오케이피트니스 연산점 헬스&amp;PT</t>
+          <t>PT의 신</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>okfitness_yeonsan@naver.com</t>
+          <t>jincau81@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1342-9791</t>
+          <t>0507-1451-0819</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 152 지하1층 B102, B101호</t>
+          <t>부산광역시 연제구 반송로 81 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.okfitness.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3894,22 +3890,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1131</v>
+        <v>66</v>
       </c>
       <c r="Q37" t="n">
-        <v>733</v>
+        <v>14</v>
       </c>
       <c r="R37" t="n">
-        <v>1864</v>
+        <v>80</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,61 +3914,61 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1322754903</t>
+          <t>1546418770</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322754903</t>
+          <t>https://m.place.naver.com/place/1546418770</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>목욕,찜질</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>럭키랜드</t>
+          <t>코오롱스포렉스 부산아시아드점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rongzel@naver.com</t>
+          <t>kolon_sporex@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>051-753-7009</t>
+          <t>0507-1474-5500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 토곡로 39 럭키랜드</t>
+          <t>부산광역시 연제구 종합운동장로 7 홈플러스 아시아드점 B2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.sporex.com/sub_branch/list_v.php?number=19</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3993,17 +3989,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="R38" t="n">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4012,51 +4008,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1422033439</t>
+          <t>1164725450</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1422033439</t>
+          <t>https://m.place.naver.com/place/1164725450</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>리드헬스&amp;PT&amp;기구필라테스 연산점24시</t>
+          <t>마이리얼바디 연산토곡점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>lead8132@naver.com</t>
+          <t>myrealbody@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1356-8132</t>
+          <t>0507-1393-9369</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로13번길 25 한창타워 3층 내 리드헬스(301호~303호)</t>
+          <t>부산광역시 연제구 고분로 234 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lead_health.pt.pilates/</t>
+          <t>https://www.youtube.com/watch?v=4cW2vAWiJC0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4082,22 +4078,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>701</v>
+        <v>40</v>
       </c>
       <c r="Q39" t="n">
-        <v>1565</v>
+        <v>18</v>
       </c>
       <c r="R39" t="n">
-        <v>2266</v>
+        <v>58</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4106,51 +4102,51 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1311686124</t>
+          <t>2079540165</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311686124</t>
+          <t>https://m.place.naver.com/place/2079540165</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>템플짐 연산점 헬스&amp;PT</t>
+          <t>원앤온리PT 부산교대점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>alswl1933@naver.com</t>
+          <t>hunkyle0104@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1368-1876</t>
+          <t>0507-1471-0290</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 163 스타메디컬빌딩 8층</t>
+          <t>부산광역시 연제구 명륜로2번길 7 3층 306호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alswl1933</t>
+          <t>https://youtube.com/@TV-cs3gl</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4165,7 +4161,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4185,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>499</v>
+        <v>56</v>
       </c>
       <c r="Q40" t="n">
-        <v>370</v>
+        <v>536</v>
       </c>
       <c r="R40" t="n">
-        <v>869</v>
+        <v>592</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4200,51 +4196,51 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2059297467</t>
+          <t>1606861644</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059297467</t>
+          <t>https://m.place.naver.com/place/1606861644</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>제이엠드림핏 헬스&amp;PT, 태닝 연산점</t>
+          <t>제로짐 피티&amp;제로 필라테스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ninopjd@naver.com</t>
+          <t>zerogym0@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>051-751-7910</t>
+          <t>0507-1435-0111</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 180 엠타워상가 3층</t>
+          <t>부산광역시 연제구 중앙대로 1033 메디컬빌딩 10층 제로필라테스/11층 제로짐</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ninopjd</t>
+          <t>https://blog.naver.com/zerogym0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4270,7 +4266,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4279,13 +4275,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>260</v>
+        <v>89</v>
       </c>
       <c r="Q41" t="n">
-        <v>304</v>
+        <v>942</v>
       </c>
       <c r="R41" t="n">
-        <v>564</v>
+        <v>1031</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4294,56 +4290,56 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1891543405</t>
+          <t>1323116558</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1891543405</t>
+          <t>https://m.place.naver.com/place/1323116558</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>베러 필라테스</t>
+          <t>피티가치 시청연산점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>betterpila@naver.com</t>
+          <t>yesiamyuy@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1407-5619</t>
+          <t>0507-1408-7550</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원남로16번길 24 3층 302호</t>
+          <t>부산광역시 연제구 중앙대로 1043 정인빌딩 5층 피티가치 시청연산점</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/betterpilates__/?igsh=MmtwYnZyNWx0dmxq</t>
+          <t>https://www.instagram.com/pt_gachi_cityhall?igshid=MzRlODBiNWFlZA==</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4353,7 +4349,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4373,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>601</v>
       </c>
       <c r="R42" t="n">
-        <v>106</v>
+        <v>825</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4388,17 +4384,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1548578360</t>
+          <t>1606361593</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548578360</t>
+          <t>https://m.place.naver.com/place/1606361593</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4410,29 +4406,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>유니크짐연산점 24시헬스PT</t>
+          <t>글래드휘트니스 시청점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2017_uniquegym@naver.com</t>
+          <t>gladfitness_cityhall@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>051-867-1088</t>
+          <t>051-868-0045</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 113-1 2층 유니크짐</t>
+          <t>부산광역시 연제구 중앙대로1043번길 34 시청역SK뷰 아파트 상가 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://uniquegym.co.kr/</t>
+          <t>https://booking.naver.com/booking/6/bizes/585952?theme=place&amp;entry=pll&amp;area=pll</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4467,13 +4463,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>338</v>
+        <v>1095</v>
       </c>
       <c r="Q43" t="n">
-        <v>294</v>
+        <v>806</v>
       </c>
       <c r="R43" t="n">
-        <v>632</v>
+        <v>1901</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4482,47 +4478,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1538954031</t>
+          <t>1703558578</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538954031</t>
+          <t>https://m.place.naver.com/place/1703558578</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>모두요가필라테스</t>
+          <t>럭키짐 PT 연산점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>everybody_yp@naver.com</t>
+          <t>luvlyjomi@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1302-4296</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 221 4층</t>
+          <t>부산광역시 연제구 과정로343번길 22 B동 3층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/modoo_yogapilates.barre</t>
+          <t>https://blog.naver.com/luvlyjomi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="R44" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,56 +4572,56 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2066412718</t>
+          <t>2009383093</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066412718</t>
+          <t>https://m.place.naver.com/place/2009383093</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>모셔너리 PT 부산교대점</t>
+          <t>퍼스트밸런스 헬스&amp;PT&amp;GX 연산점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>motionary@naver.com</t>
+          <t>balancebody_sasang@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1315-6550</t>
+          <t>0507-1412-2329</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 교대로24번길 7 3층</t>
+          <t>부산광역시 연제구 신금로 25 노블레스스퀘어 B1층 퍼스트밸런스 연산</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://motionary.imweb.me/</t>
+          <t>https://www.instagram.com/firstbalance_center/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4642,7 +4642,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4651,13 +4651,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="Q45" t="n">
-        <v>53</v>
+        <v>1032</v>
       </c>
       <c r="R45" t="n">
-        <v>131</v>
+        <v>1150</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,51 +4666,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2082500011</t>
+          <t>1163168113</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082500011</t>
+          <t>https://m.place.naver.com/place/1163168113</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>트렌드핏 피트니스 헬스&amp;PT 연산점</t>
+          <t>플랜핏 헬스 &amp; PT 연산점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>qkrwnsgud67@naver.com</t>
+          <t>ryul727@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1374-8141</t>
+          <t>0507-1349-7027</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 144 8층 트렌드핏</t>
+          <t>부산광역시 연제구 월드컵대로145번길 32 4층 플랜핏 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/trendfit_yeonsan?igsh=a3ZudTYxNGsxNm5h</t>
+          <t>https://open.kakao.com/o/sWHh2dTb</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4736,7 +4736,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>521</v>
+        <v>280</v>
       </c>
       <c r="Q46" t="n">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="R46" t="n">
-        <v>888</v>
+        <v>700</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4760,51 +4760,47 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1413356192</t>
+          <t>1110009452</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1413356192</t>
+          <t>https://m.place.naver.com/place/1110009452</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>원더핏1대1PT 부산시청점</t>
+          <t>247복싱</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jc4rpav9@naver.com</t>
+          <t>thaikick@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1399-0184</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1037 2층</t>
+          <t>부산광역시 연제구 거제대로 172</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonderfit__official</t>
+          <t>https://blog.naver.com/thaikick/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4819,7 +4815,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4835,17 +4831,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="Q47" t="n">
         <v>68</v>
       </c>
       <c r="R47" t="n">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4854,17 +4850,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1925927850</t>
+          <t>501106950</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925927850</t>
+          <t>https://m.place.naver.com/place/501106950</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4876,29 +4872,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>리오 피트니스</t>
+          <t>거제동 재활의신 타임피트니스 피티&amp;헬스장</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sangs1789@naver.com</t>
+          <t>time_fit@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1378-8377</t>
+          <t>0507-1493-3211</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 128 지하 1층</t>
+          <t>부산광역시 연제구 법원로32번길 10 협성프라자 지하1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mad_leofitness?igsh=MXNmY2RwYzRmNm9sZA%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/time_fit</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4913,7 +4909,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4933,13 +4929,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4948,17 +4944,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1808486603</t>
+          <t>1044928581</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808486603</t>
+          <t>https://m.place.naver.com/place/1044928581</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4970,34 +4966,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엠씨피트니스&amp;기구필라테스 연산점</t>
+          <t>매드맥스짐 연산점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mcfitnessyeonsan@naver.com</t>
+          <t>chaemingming-@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1421-0460</t>
+          <t>0507-1437-3848</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 152 연산빌딩 3층</t>
+          <t>부산광역시 연제구 월드컵대로 128 행복한메디컬센터 지하1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gdRSs/chat</t>
+          <t>https://www.instagram.com/mad__jackal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5018,7 +5014,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5027,13 +5023,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1092</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="n">
-        <v>801</v>
+        <v>258</v>
       </c>
       <c r="R49" t="n">
-        <v>1893</v>
+        <v>286</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5042,51 +5038,51 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1678635952</t>
+          <t>1771981270</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678635952</t>
+          <t>https://m.place.naver.com/place/1771981270</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>올데이짐 헬스&amp;PT 연산</t>
+          <t>굿라이프 스트레치</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>babuperk1@naver.com</t>
+          <t>y0uuu@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>051-866-8834</t>
+          <t>0507-1439-0166</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 256 3층 올데이짐</t>
+          <t>부산광역시 연제구 신금로 25 219호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/babuperk1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5096,12 +5092,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5121,13 +5117,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R50" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5136,56 +5132,56 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>16717118</t>
+          <t>2089437251</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16717118</t>
+          <t>https://m.place.naver.com/place/2089437251</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KN피트니스 법원</t>
+          <t>신디 필라테스&amp;PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tgloveheyyo@naver.com</t>
+          <t>cindy_pila_pt@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1429-7337</t>
+          <t>0507-1348-6864</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원로 2 고성빌딩 2층</t>
+          <t>부산광역시 연제구 월드컵대로 54 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WxkCtu</t>
+          <t>https://blog.naver.com/cindy_pila_pt</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5195,7 +5191,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5206,22 +5202,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="Q51" t="n">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="R51" t="n">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5230,51 +5226,51 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>35993162</t>
+          <t>1694109028</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35993162</t>
+          <t>https://m.place.naver.com/place/1694109028</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>피부,체형관리</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>머슬하모니</t>
+          <t>24시헬스포유</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>muscleharmony@naver.com</t>
+          <t>groupcircuit@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>051-913-1117</t>
+          <t>0507-1345-8648</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신촌로 51 지하1층</t>
+          <t>부산광역시 연제구 미남로 11 영주빌딩 4층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/groupcircuit</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5284,12 +5280,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5309,13 +5305,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5324,56 +5320,52 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1819908137</t>
+          <t>1065272252</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819908137</t>
+          <t>https://m.place.naver.com/place/1065272252</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스페이스PT&amp;헬스 시청연산점</t>
+          <t>SY피트니스짐</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>spacept@naver.com</t>
+          <t>yujupila_sy@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1498-7935</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1077 12층</t>
+          <t>부산광역시 연제구 토곡로 29 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sjo5jMMf</t>
+          <t>http://cafe.naver.com/lgfitness/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5383,7 +5375,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5394,22 +5386,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>321</v>
+        <v>7</v>
       </c>
       <c r="R53" t="n">
-        <v>408</v>
+        <v>10</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5418,51 +5410,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2018417908</t>
+          <t>11368992</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018417908</t>
+          <t>https://m.place.naver.com/place/11368992</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>더스피닝 본점 &amp; PT 연산점</t>
+          <t>모션핏피트니스 헬스&amp;PT 연산토곡점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thespinningyeonsan@naver.com</t>
+          <t>motionfit@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1401-8936</t>
+          <t>0507-1353-5528</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 190 4층</t>
+          <t>부산광역시 연제구 연안로 19 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thespinning</t>
+          <t>https://www.instagram.com/motionfit.fitness/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5497,13 +5489,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>426</v>
+        <v>542</v>
       </c>
       <c r="Q54" t="n">
-        <v>475</v>
+        <v>213</v>
       </c>
       <c r="R54" t="n">
-        <v>901</v>
+        <v>755</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5512,51 +5504,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1657255148</t>
+          <t>1531367968</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657255148</t>
+          <t>https://m.place.naver.com/place/1531367968</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>바디메디필라테스</t>
+          <t>팬덤짐PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dreambodynsol_cn@naver.com</t>
+          <t>gusco2180@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>051-851-0111</t>
+          <t>0507-1447-9683</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 130 상가A동 201호</t>
+          <t>부산광역시 연제구 세병로 10-1 2층 연산동 PT 팬덤짐 PT 헬스</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/bodymedi_pilates</t>
+          <t>https://blog.naver.com/gusco2180</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5571,7 +5563,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5591,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>645</v>
       </c>
       <c r="R55" t="n">
-        <v>51</v>
+        <v>801</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,51 +5598,51 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1421677552</t>
+          <t>1237805997</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421677552</t>
+          <t>https://m.place.naver.com/place/1237805997</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>목욕,찜질</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>매드맥스짐 연산점</t>
+          <t>럭키랜드</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>dnjsude926@naver.com</t>
+          <t>bettertoday_7@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1437-3848</t>
+          <t>051-753-7009</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 128 행복한메디컬센터 지하1층</t>
+          <t>부산광역시 연제구 토곡로 39 럭키랜드</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mad__jackal</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5660,7 +5652,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5681,17 +5673,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="Q56" t="n">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="R56" t="n">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,17 +5692,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1771981270</t>
+          <t>1422033439</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771981270</t>
+          <t>https://m.place.naver.com/place/1422033439</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5722,39 +5714,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>원앤온리PT 부산교대점</t>
+          <t>카이트운동센터</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>hunkyle0104@naver.com</t>
+          <t>sonh9882@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1471-0290</t>
+          <t>051-867-7700</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 명륜로2번길 7 3층 306호</t>
+          <t>부산광역시 연제구 시청로32번길 24 2층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://youtube.com/@TV-cs3gl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5775,17 +5767,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="Q57" t="n">
-        <v>528</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>584</v>
+        <v>43</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5794,56 +5786,56 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1606861644</t>
+          <t>37464088</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1606861644</t>
+          <t>https://m.place.naver.com/place/37464088</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>국제휘트니스 &amp; PT 교대점</t>
+          <t>노블레스짐 PT&amp;스트레칭</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kukje_fitness@naver.com</t>
+          <t>lllooo1024@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1496-7969</t>
+          <t>0507-1383-0097</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1217 국제빌딩 지하1층</t>
+          <t>부산광역시 연제구 신금로 25 2층 220호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@%EA%B5%AD%ED%97%AC%EB%B6%80%EC%82%B0%EA%B5%90%EB%8C%80%EC%A0%90</t>
+          <t>https://www.instagram.com/noblessegym</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5853,7 +5845,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5873,13 +5865,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>475</v>
+        <v>31</v>
       </c>
       <c r="Q58" t="n">
-        <v>495</v>
+        <v>352</v>
       </c>
       <c r="R58" t="n">
-        <v>970</v>
+        <v>383</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5888,17 +5880,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>32565643</t>
+          <t>1152978393</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32565643</t>
+          <t>https://m.place.naver.com/place/1152978393</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5910,29 +5902,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>굿라이프 스트레치</t>
+          <t>탑조이PT 연산점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>y0uuu@naver.com</t>
+          <t>tnghks9702@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1439-0166</t>
+          <t>0507-1489-9702</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 25 219호</t>
+          <t>부산광역시 연제구 월드컵대로 3 B1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/s0__0hwan?igsh=cXg3b3kyem54dmky&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5942,7 +5934,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5963,17 +5955,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>402</v>
       </c>
       <c r="R59" t="n">
-        <v>17</v>
+        <v>474</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5982,17 +5974,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2089437251</t>
+          <t>1984112260</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089437251</t>
+          <t>https://m.place.naver.com/place/1984112260</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6004,34 +5996,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>플랜핏 헬스 &amp; PT 연산점</t>
+          <t>원더핏1대1PT 부산시청점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ryul727@naver.com</t>
+          <t>jc4rpav9@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1349-7027</t>
+          <t>0507-1399-0184</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로145번길 32 4층 플랜핏 헬스&amp;PT 연산점</t>
+          <t>부산광역시 연제구 중앙대로 1037 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWHh2dTb</t>
+          <t>https://www.instagram.com/wonderfit__official</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6052,7 +6044,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6061,13 +6053,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="Q60" t="n">
-        <v>440</v>
+        <v>68</v>
       </c>
       <c r="R60" t="n">
-        <v>719</v>
+        <v>131</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6076,51 +6068,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1110009452</t>
+          <t>1925927850</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110009452</t>
+          <t>https://m.place.naver.com/place/1925927850</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>헤비핸즈복싱</t>
+          <t>더스피닝 본점 &amp; PT 연산점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hardtokilll@naver.com</t>
+          <t>thespinningyeonsan@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1324-0652</t>
+          <t>0507-1401-8936</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 314 B동 3층 301호</t>
+          <t>부산광역시 연제구 과정로 190 4층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heavyhands_boxing</t>
+          <t>https://www.instagram.com/thespinning</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6155,13 +6147,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>480</v>
       </c>
       <c r="R61" t="n">
-        <v>7</v>
+        <v>909</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6170,56 +6162,56 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1403278642</t>
+          <t>1657255148</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403278642</t>
+          <t>https://m.place.naver.com/place/1657255148</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>마이리얼바디 연산토곡점</t>
+          <t>바디로운필라테스 연산점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>myrealbody@naver.com</t>
+          <t>bodyroun6@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1393-9369</t>
+          <t>0507-1333-6952</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 234 3층</t>
+          <t>부산광역시 연제구 과정로 180 4층 402호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4cW2vAWiJC0</t>
+          <t>https://bodyrounpilates.com</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6240,22 +6232,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="R62" t="n">
-        <v>54</v>
+        <v>379</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6264,17 +6256,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2079540165</t>
+          <t>1972142834</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079540165</t>
+          <t>https://m.place.naver.com/place/1972142834</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6286,29 +6278,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>럭키짐 PT 연산점</t>
+          <t>금메달짐PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>luvlyjomi@naver.com</t>
+          <t>coachcho13@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1302-4296</t>
+          <t>0507-1306-8147</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 22 B동 3층</t>
+          <t>부산광역시 연제구 거제천로269번길 44 지층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luvlyjomi</t>
+          <t>https://blog.naver.com/coachcho13</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6343,13 +6335,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Q63" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="R63" t="n">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6358,51 +6350,51 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2009383093</t>
+          <t>1556823527</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009383093</t>
+          <t>https://m.place.naver.com/place/1556823527</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>무지개휘트니스 연산점 헬스&amp;PT&amp;GX</t>
+          <t>래피드스튜디오GYM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rainbow4445@naver.com</t>
+          <t>rapidstudio@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1346-4445</t>
+          <t>0507-1422-3351</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1090 5층 무지개휘트니스</t>
+          <t>부산광역시 연제구 시청로 20 이레빌딩 6층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rainbow4445</t>
+          <t>https://blog.naver.com/rapidstudio</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6437,13 +6429,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>940</v>
+        <v>105</v>
       </c>
       <c r="Q64" t="n">
-        <v>970</v>
+        <v>277</v>
       </c>
       <c r="R64" t="n">
-        <v>1910</v>
+        <v>382</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,56 +6444,56 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1247782660</t>
+          <t>36084249</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247782660</t>
+          <t>https://m.place.naver.com/place/36084249</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>바디로운필라테스 연산점</t>
+          <t>유니크짐연산점 24시헬스PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bodyroun6@naver.com</t>
+          <t>2017_uniquegym@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1333-6952</t>
+          <t>051-867-1088</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 180 4층 402호</t>
+          <t>부산광역시 연제구 연수로 113-1 2층 유니크짐</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://bodyrounpilates.com</t>
+          <t>https://uniquegym.co.kr/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6511,7 +6503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6531,13 +6523,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>226</v>
+        <v>339</v>
       </c>
       <c r="Q65" t="n">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="R65" t="n">
-        <v>389</v>
+        <v>636</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6546,17 +6538,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1972142834</t>
+          <t>1538954031</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972142834</t>
+          <t>https://m.place.naver.com/place/1538954031</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6568,29 +6560,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>유코어바레&amp;필라테스</t>
+          <t>유코어필라테스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ks-0278@naver.com</t>
+          <t>ucorepilates@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1317-6055</t>
+          <t>0507-1370-5882</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 346 3층</t>
+          <t>부산광역시 연제구 과정로 345 2층 유코어필라테스</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ks-0278</t>
+          <t>https://www.instagram.com/ucore_pilates?igsh=aDA0cmxmY3hlNDFn</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6605,7 +6597,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6625,13 +6617,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="Q66" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6640,17 +6632,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1145351665</t>
+          <t>2085675391</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145351665</t>
+          <t>https://m.place.naver.com/place/2085675391</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6662,25 +6654,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>킥앤핏스튜디오</t>
+          <t>자연안에PT스튜디오</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>schlgud@naver.com</t>
+          <t>sdud6040@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1429-8805</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로46번길 15 상가동 202호</t>
+          <t>부산광역시 연제구 월드컵대로 141</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kick_fit_studio?igsh=N3p3dmRsYm4wZWFr</t>
+          <t>http://www.naturept.co.kr/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6715,13 +6711,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="R67" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,52 +6726,56 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2007111294</t>
+          <t>38757600</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007111294</t>
+          <t>https://m.place.naver.com/place/38757600</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코어핏 스튜디오 PT/헬스</t>
+          <t>스탠다드짐 연산토곡점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>qkzp2447@naver.com</t>
+          <t>standardgym@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1325-2235</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 세병로 16 한성기린아파트 상가3층 302호</t>
+          <t>부산광역시 연제구 고분로236번길 13 지하1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Bodysmith</t>
+          <t>https://www.instagram.com/standardgym___4/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6805,13 +6805,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="Q68" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R68" t="n">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6820,66 +6820,66 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1238470397</t>
+          <t>2056534999</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1238470397</t>
+          <t>https://m.place.naver.com/place/2056534999</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PT의 신</t>
+          <t>모셔너리 PT 부산교대점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>intogym@naver.com</t>
+          <t>motionary@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1451-0819</t>
+          <t>0507-1315-6550</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 81 2층</t>
+          <t>부산광역시 연제구 교대로24번길 7 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://motionary.imweb.me/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6890,22 +6890,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="Q69" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="R69" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6914,51 +6914,51 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1546418770</t>
+          <t>2082500011</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546418770</t>
+          <t>https://m.place.naver.com/place/2082500011</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>신디 필라테스&amp;PT</t>
+          <t>트렌드핏 피트니스 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>cindy_pila_pt@naver.com</t>
+          <t>headvicjo_fitbeom@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1348-6864</t>
+          <t>0507-1374-8141</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 54 3층</t>
+          <t>부산광역시 연제구 과정로 144 8층 트렌드핏</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cindy_pila_pt</t>
+          <t>https://www.instagram.com/trendfit_yeonsan?igsh=a3ZudTYxNGsxNm5h</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6989,17 +6989,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>74</v>
+        <v>523</v>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>368</v>
       </c>
       <c r="R70" t="n">
-        <v>84</v>
+        <v>891</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7008,61 +7008,57 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1694109028</t>
+          <t>1413356192</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1694109028</t>
+          <t>https://m.place.naver.com/place/1413356192</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>글래드휘트니스 시청점</t>
+          <t>어메이징골프아카데미</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gladfitness_cityhall@naver.com</t>
+          <t>aggolf@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>051-868-0045</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 34 시청역SK뷰 아파트 상가 3층</t>
+          <t>부산광역시 연제구 중앙대로 1042 12층, 13층, 14층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/585952?theme=place&amp;entry=pll&amp;area=pll</t>
+          <t>https://blog.naver.com/aggolf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7087,13 +7083,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1095</v>
+        <v>261</v>
       </c>
       <c r="Q71" t="n">
-        <v>797</v>
+        <v>73</v>
       </c>
       <c r="R71" t="n">
-        <v>1892</v>
+        <v>334</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7102,17 +7098,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1703558578</t>
+          <t>1876155285</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703558578</t>
+          <t>https://m.place.naver.com/place/1876155285</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7124,29 +7120,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>온스트레치 KN피트니스 법원점</t>
+          <t>벨라테스앤피티</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>tgloveheyyo@naver.com</t>
+          <t>bellates_pt@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1343-0432</t>
+          <t>0507-1365-3106</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원로 2 3층</t>
+          <t>부산광역시 연제구 아시아드대로 42 2층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bellates_pt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7156,12 +7152,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7177,17 +7173,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7196,17 +7192,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2040167591</t>
+          <t>1187844272</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040167591</t>
+          <t>https://m.place.naver.com/place/1187844272</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7218,29 +7214,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>보답피트니스 시청 헬스&amp;PT</t>
+          <t>첼시 피트니스 시청점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>fandomfit_cityhall@naver.com</t>
+          <t>chelsea_sicheong@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1311-8578</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 94 6층, 7층</t>
+          <t>부산광역시 연제구 시청로 6 포스코더샾애비뉴1차 101동 상가 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodapfitness</t>
+          <t>https://blog.naver.com/chelsea_sicheong</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7255,7 +7247,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7275,13 +7267,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>512</v>
+        <v>249</v>
       </c>
       <c r="Q73" t="n">
-        <v>681</v>
+        <v>273</v>
       </c>
       <c r="R73" t="n">
-        <v>1193</v>
+        <v>522</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7290,56 +7282,60 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1014850411</t>
+          <t>1941598768</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014850411</t>
+          <t>https://m.place.naver.com/place/1941598768</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>금메달짐</t>
+          <t>케어스튜디오 체형교정 &amp; PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>coachcho13@naver.com</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>takho092753@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>takho092753@gmail.com</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1306-8147</t>
+          <t>0507-1303-5542</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로269번길 44 지층</t>
+          <t>부산광역시 연제구 중앙대로1124번길 20 서진빌딩 3층 케어스튜디오</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coachcho13</t>
+          <t>https://physiograph.kr</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7369,13 +7365,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="Q74" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="R74" t="n">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7384,47 +7380,51 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1556823527</t>
+          <t>1088942032</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1556823527</t>
+          <t>https://m.place.naver.com/place/1088942032</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>첼시 피트니스 시청점</t>
+          <t>잼피티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>chelsea_sicheong@naver.com</t>
+          <t>jam__pt@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1423-9395</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 6 포스코더샾애비뉴1차 101동 상가 2층</t>
+          <t>부산광역시 연제구 연수로 150 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chelsea_sicheong</t>
+          <t>https://www.instagram.com/jam__pt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="Q75" t="n">
-        <v>248</v>
+        <v>30</v>
       </c>
       <c r="R75" t="n">
-        <v>493</v>
+        <v>144</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7474,17 +7474,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1941598768</t>
+          <t>1040929885</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941598768</t>
+          <t>https://m.place.naver.com/place/1040929885</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7496,29 +7496,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>유코어필라테스</t>
+          <t>유코어바레&amp;필라테스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ucorepilates@naver.com</t>
+          <t>ks-0278@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1370-5882</t>
+          <t>0507-1317-6055</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 345 2층 유코어필라테스</t>
+          <t>부산광역시 연제구 과정로 346 3층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ucore_pilates?igsh=aDA0cmxmY3hlNDFn</t>
+          <t>https://blog.naver.com/ks-0278</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R76" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7568,17 +7568,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2085675391</t>
+          <t>1145351665</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085675391</t>
+          <t>https://m.place.naver.com/place/1145351665</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7590,34 +7590,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>스탠다드짐 연산토곡점</t>
+          <t>KN피트니스 법원</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>standardgym@naver.com</t>
+          <t>tgloveheyyo@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1325-2235</t>
+          <t>0507-1429-7337</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로236번길 13 지하1층</t>
+          <t>부산광역시 연제구 법원로 2 고성빌딩 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/standard_gym4/</t>
+          <t>http://pf.kakao.com/_WxkCtu</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7638,7 +7638,7 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7647,13 +7647,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Q77" t="n">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="R77" t="n">
-        <v>284</v>
+        <v>384</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7662,17 +7662,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>2056534999</t>
+          <t>35993162</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056534999</t>
+          <t>https://m.place.naver.com/place/35993162</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7684,39 +7684,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>인트로피트니스 연산점 24시 헬스&amp;PT</t>
+          <t>오케이피트니스 연산점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>intro_fitness@naver.com</t>
+          <t>okfitness_yeonsan@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1490-9696</t>
+          <t>0507-1342-9791</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 89 BS89빌딩 5층 인트로피트니스 연산점</t>
+          <t>부산광역시 연제구 월드컵대로 152 지하1층 B102, B101호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/intro_fitness</t>
+          <t>https://www.okfitness.co.kr</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7732,7 +7732,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>508</v>
+        <v>1183</v>
       </c>
       <c r="Q78" t="n">
-        <v>518</v>
+        <v>741</v>
       </c>
       <c r="R78" t="n">
-        <v>1026</v>
+        <v>1924</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7756,17 +7756,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1710235102</t>
+          <t>1322754903</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710235102</t>
+          <t>https://m.place.naver.com/place/1322754903</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7778,29 +7778,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>더리얼기구필라테스&amp;PT 연산점</t>
+          <t>베러 필라테스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kch9728kkk@naver.com</t>
+          <t>betterpila@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>051-868-3948</t>
+          <t>0507-1407-5619</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로73번길 84 더리얼기구필라테스&amp;PT 연산점</t>
+          <t>부산광역시 연제구 법원남로16번길 24 3층 302호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/therealpilates_pt/</t>
+          <t>https://www.instagram.com/betterpilates__/?igsh=MmtwYnZyNWx0dmxq</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7835,13 +7835,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="Q79" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R79" t="n">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7850,17 +7850,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1560928411</t>
+          <t>1548578360</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1560928411</t>
+          <t>https://m.place.naver.com/place/1548578360</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
